--- a/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,79 +700,127 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3374</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>3181</v>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>6555</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11653</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>69908</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>76185</v>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>146093</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>73282</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69908</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>79366</v>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>76185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>152648</v>
+          <t>69645</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>78580</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>146093</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>139198</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>149665</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Cadiz</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>9519</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73282</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>7782</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>17301</v>
+          <t>79366</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79366</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>152648</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>117320</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7431</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>119814</v>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>237134</v>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8952</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>11867</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>19662</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>126839</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>127596</v>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>254435</v>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>11486</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Cordoba</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>6421</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117320</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>110687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>122713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>5768</v>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,75%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>145</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>12189</v>
+          <t>113310</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>123728</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>237134</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>228586</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>243707</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>51847</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126839</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>61395</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>127596</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>113242</v>
+          <t>127596</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>127596</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>254435</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>58268</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>67163</v>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,05%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>125431</v>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>9710</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>15812</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4084</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>6845</v>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>549</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>10929</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>66059</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51847</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>71289</v>
+          <t>88,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>137349</v>
+          <t>56346</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>64552</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>113242</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>106994</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>118117</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>70143</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58268</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>78134</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>67163</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>148278</v>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>125431</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>3514</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>2806</v>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>6319</v>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14123</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6821</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>17920</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>30999</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>37913</v>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>68913</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1677,216 +2309,342 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>34513</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66059</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>61299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>40719</v>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>87,39%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>75232</v>
+          <t>62391</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>75695</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>137349</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>127264</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>142896</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>85,83%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Jaen</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>4136</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70143</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>10042</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>14179</v>
+          <t>78134</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>78134</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>148278</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>42031</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>46144</v>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>88174</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>8522</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1894,145 +2652,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46167</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>56186</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>102353</v>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4342</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>12233</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30999</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>13925</v>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>26159</v>
+          <t>34840</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>39683</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>68913</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>64679</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>71807</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -2040,216 +2878,342 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>112275</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>34513</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>142087</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>40719</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>317</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>254361</v>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>124508</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>156012</v>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>354</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>280520</v>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>13992</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>15,97%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>17685</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>3990</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>8755</v>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>12745</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2260,67 +3224,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>127629</v>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>42031</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>148040</v>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>275669</v>
+          <t>40741</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>82,13%</t>
+        </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>88174</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>81892</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>92927</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>86,15%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>80,01%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -2331,20 +3337,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>131619</v>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>46167</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2352,32 +3362,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>156795</v>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>288414</v>
+          <t>56186</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>56186</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -2390,6 +3408,36 @@
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>102353</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2398,75 +3446,117 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>47272</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7080</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>59103</v>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>5580</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>17821</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>17043</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10191</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>24594</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>106375</v>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -2474,70 +3564,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>865</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>618068</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>897</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>702869</v>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1762</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>1320937</v>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>9007</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>16150</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -2545,75 +3677,1142 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>665340</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>112275</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>116712</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>761972</v>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>85,37%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>142087</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1919</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>1427312</v>
+          <t>133443</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>147577</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>91,07%</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>254361</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>245347</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>262502</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>124508</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>156012</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>156012</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>156012</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>280520</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>280520</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>280520</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>6755</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>4158</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>13767</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4327</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>5077</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>127629</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>123601</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>129669</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>148040</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>142030</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>152023</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>275669</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>268846</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>280327</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>131619</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>156795</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>288414</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>23273</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>33747</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>63860</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>95162</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>22171</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>8264</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>20251</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>38405</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>618068</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>606023</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>629362</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>91,08%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>702869</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>687116</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>714365</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1320937</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>1300177</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>1337647</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -2621,19 +4820,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>65020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72412</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69645</t>
+          <t>70433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78580</t>
+          <t>78564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139198</t>
+          <t>139866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110687</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122713</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113310</t>
+          <t>113535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123728</t>
+          <t>123822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228586</t>
+          <t>228650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243707</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>54925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>64522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106994</t>
+          <t>106696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118117</t>
+          <t>117918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>61520</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>68696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75695</t>
+          <t>76229</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127264</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142896</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64679</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71807</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>44312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81892</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106287</t>
+          <t>106590</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116712</t>
+          <t>117212</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133443</t>
+          <t>133793</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147577</t>
+          <t>147655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>244169</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>262502</t>
+          <t>261670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>438</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>123601</t>
+          <t>123803</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>129669</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>141953</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>152023</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>268846</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>280377</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>65252</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>95162</t>
+          <t>95291</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3899</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61476</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56980</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69908</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65020</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76185</t>
+          <t>53447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70433</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78564</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146093</t>
+          <t>114923</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>139866</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149789</t>
+          <t>117795</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3879</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8138</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7431</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13397</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2973</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7990</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5742</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108984</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103641</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>112283</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>117320</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>111071</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>122849</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>119814</t>
+          <t>90789</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113535</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123822</t>
+          <t>94961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>237134</t>
+          <t>199772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228650</t>
+          <t>190793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244338</t>
+          <t>205532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5047</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54327</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49846</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57072</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51847</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47387</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54925</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61395</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64522</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>113242</t>
+          <t>104886</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106696</t>
+          <t>99571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117918</t>
+          <t>109472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2314,67 +2314,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>65454</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56725</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70312</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>78,61%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>66059</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>61520</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>68696</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71289</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>60831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76229</t>
+          <t>69117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>137349</t>
+          <t>131864</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127695</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>137630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3621</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3514</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6509</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1644</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>36770</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33324</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>38492</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>30999</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>28004</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81,14%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37913</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>28766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39653</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>68913</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64416</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>71694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7784</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4661</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12593</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>25,73%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6458</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>893</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>40264</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>35426</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>43622</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>72,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>42031</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>37945</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>44312</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>41682</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50313</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>81946</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>76809</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9816</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>16801</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>7080</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>11791</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9657</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9858</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>127460</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>119699</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>133291</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>84,67%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>94,29%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>112275</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>106590</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>117212</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>85,61%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>94,14%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>142087</t>
+          <t>110285</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133793</t>
+          <t>103760</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>114698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>254361</t>
+          <t>237745</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>244169</t>
+          <t>227349</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261670</t>
+          <t>245541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3912,72 +3912,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>13760</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>8,63%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4025,72 +4025,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>384</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4138,72 +4138,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>150691</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>144541</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>154878</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>127629</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>123803</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>129670</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>148040</t>
+          <t>137037</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>141953</t>
+          <t>133347</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>151956</t>
+          <t>138957</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>275669</t>
+          <t>287729</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>268659</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280377</t>
+          <t>292646</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4368,72 +4368,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>42278</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>31638</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>56786</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>32551</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>24459</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>42378</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>65252</t>
+          <t>61127</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>95291</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -4481,72 +4481,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>20665</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>9523</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>21824</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>865</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>618068</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>606801</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>628324</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>582184</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>569808</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592488</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1320937</t>
+          <t>1227609</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1301380</t>
+          <t>1209389</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1337289</t>
+          <t>1243691</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
